--- a/03_Outputs/all/03_DS/ds_idx11_pobreza.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx11_pobreza.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.217690973400962</v>
+        <v>2.217690973400964</v>
       </c>
       <c r="D2">
-        <v>-2.362131911236126</v>
+        <v>-2.362131911236127</v>
       </c>
       <c r="E2">
-        <v>-0.8706692706572419</v>
+        <v>-0.8706692706572616</v>
       </c>
       <c r="F2">
-        <v>-0.7335996787745469</v>
+        <v>-0.7335996787745238</v>
       </c>
       <c r="G2">
-        <v>-0.5499024256093564</v>
+        <v>-0.5499024256093565</v>
       </c>
     </row>
     <row r="3">
@@ -433,16 +433,16 @@
         <v>-1.852320403982484</v>
       </c>
       <c r="D3">
-        <v>-1.400677162124889</v>
+        <v>-1.400677162124892</v>
       </c>
       <c r="E3">
-        <v>-0.7989436479829528</v>
+        <v>-0.7989436479829798</v>
       </c>
       <c r="F3">
-        <v>-0.9906364112492833</v>
+        <v>-0.990636411249262</v>
       </c>
       <c r="G3">
-        <v>-0.2756701026612123</v>
+        <v>-0.2756701026612115</v>
       </c>
     </row>
     <row r="4">
@@ -460,16 +460,16 @@
         <v>2.588933119157866</v>
       </c>
       <c r="D4">
-        <v>-0.9500134472505469</v>
+        <v>-0.9500134472505466</v>
       </c>
       <c r="E4">
-        <v>-1.072003581634872</v>
+        <v>-1.072003581634837</v>
       </c>
       <c r="F4">
-        <v>1.322226786805705</v>
+        <v>1.322226786805734</v>
       </c>
       <c r="G4">
-        <v>0.8829575626291845</v>
+        <v>0.8829575626291852</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.3449889226073375</v>
+        <v>-0.3449889226073376</v>
       </c>
       <c r="D5">
-        <v>0.7300506152513294</v>
+        <v>0.7300506152513291</v>
       </c>
       <c r="E5">
-        <v>-3.834816743794814</v>
+        <v>-3.83481674379479</v>
       </c>
       <c r="F5">
-        <v>0.8904758439406107</v>
+        <v>0.8904758439407093</v>
       </c>
       <c r="G5">
-        <v>-0.6551034470845002</v>
+        <v>-0.6551034470845006</v>
       </c>
     </row>
     <row r="6">
@@ -517,13 +517,13 @@
         <v>-0.7247530556717896</v>
       </c>
       <c r="E6">
-        <v>-0.1690475686111922</v>
+        <v>-0.1690475686111841</v>
       </c>
       <c r="F6">
-        <v>0.3251499709208934</v>
+        <v>0.3251499709208973</v>
       </c>
       <c r="G6">
-        <v>0.4099110871915359</v>
+        <v>0.4099110871915356</v>
       </c>
     </row>
     <row r="7">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3599740314329102</v>
+        <v>0.3599740314329107</v>
       </c>
       <c r="D7">
-        <v>1.818274559830091</v>
+        <v>1.818274559830092</v>
       </c>
       <c r="E7">
-        <v>0.5281191789983425</v>
+        <v>0.5281191789983353</v>
       </c>
       <c r="F7">
-        <v>-0.2534775150132567</v>
+        <v>-0.2534775150132718</v>
       </c>
       <c r="G7">
         <v>1.376400311029675</v>
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>1.517561766944162</v>
+        <v>1.517561766944163</v>
       </c>
       <c r="D8">
-        <v>0.2749409382225211</v>
+        <v>0.2749409382225217</v>
       </c>
       <c r="E8">
-        <v>1.108885024030943</v>
+        <v>1.108885024030947</v>
       </c>
       <c r="F8">
-        <v>0.2050638682565846</v>
+        <v>0.2050638682565539</v>
       </c>
       <c r="G8">
-        <v>-0.6535587625076835</v>
+        <v>-0.6535587625076837</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         <v>1.998167464452126</v>
       </c>
       <c r="D9">
-        <v>0.5266812193307879</v>
+        <v>0.5266812193307886</v>
       </c>
       <c r="E9">
-        <v>1.574196472914217</v>
+        <v>1.574196472914209</v>
       </c>
       <c r="F9">
-        <v>-0.2752417353216208</v>
+        <v>-0.2752417353216633</v>
       </c>
       <c r="G9">
-        <v>0.347444397778975</v>
+        <v>0.3474443977789745</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-2.602793855070576</v>
+        <v>-2.602793855070577</v>
       </c>
       <c r="D10">
-        <v>3.399833656833151</v>
+        <v>3.399833656833152</v>
       </c>
       <c r="E10">
-        <v>-1.38593334301467</v>
+        <v>-1.385933343014615</v>
       </c>
       <c r="F10">
-        <v>2.063806709764271</v>
+        <v>2.063806709764303</v>
       </c>
       <c r="G10">
-        <v>-0.5933169348484082</v>
+        <v>-0.593316934848409</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.4255898130840948</v>
+        <v>-0.4255898130840945</v>
       </c>
       <c r="D11">
-        <v>0.3582948198792785</v>
+        <v>0.3582948198792788</v>
       </c>
       <c r="E11">
-        <v>2.459530411117434</v>
+        <v>2.459530411117427</v>
       </c>
       <c r="F11">
-        <v>-0.2218951883678029</v>
+        <v>-0.2218951883678669</v>
       </c>
       <c r="G11">
-        <v>2.194565398294835</v>
+        <v>2.194565398294836</v>
       </c>
     </row>
     <row r="12">
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.6564236495197474</v>
+        <v>-0.6564236495197475</v>
       </c>
       <c r="D12">
         <v>-1.623052179688812</v>
       </c>
       <c r="E12">
-        <v>-0.8568772359790066</v>
+        <v>-0.8568772359789947</v>
       </c>
       <c r="F12">
-        <v>0.4952711917838232</v>
+        <v>0.4952711917838447</v>
       </c>
       <c r="G12">
         <v>-1.250806853467373</v>
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>2.086641144892488</v>
+        <v>2.086641144892489</v>
       </c>
       <c r="D13">
-        <v>4.010679641733057</v>
+        <v>4.010679641733059</v>
       </c>
       <c r="E13">
-        <v>0.2140417387695755</v>
+        <v>0.2140417387696004</v>
       </c>
       <c r="F13">
-        <v>0.9680643635004822</v>
+        <v>0.9680643635004719</v>
       </c>
       <c r="G13">
-        <v>-1.224065423988815</v>
+        <v>-1.224065423988816</v>
       </c>
     </row>
     <row r="14">
@@ -730,13 +730,13 @@
         <v>-2.248368434954414</v>
       </c>
       <c r="D14">
-        <v>-2.876114385129798</v>
+        <v>-2.876114385129803</v>
       </c>
       <c r="E14">
-        <v>-0.5275285461793533</v>
+        <v>-0.5275285461794331</v>
       </c>
       <c r="F14">
-        <v>-2.955266282030001</v>
+        <v>-2.955266282029987</v>
       </c>
       <c r="G14">
         <v>-1.078661829933573</v>
@@ -757,16 +757,16 @@
         <v>-10.6709885080744</v>
       </c>
       <c r="D15">
-        <v>-0.4351337764813774</v>
+        <v>-0.4351337764813815</v>
       </c>
       <c r="E15">
-        <v>2.776563299735511</v>
+        <v>2.776563299735498</v>
       </c>
       <c r="F15">
-        <v>-0.4122383689068824</v>
+        <v>-0.4122383689069562</v>
       </c>
       <c r="G15">
-        <v>0.888668517899658</v>
+        <v>0.8886685178996612</v>
       </c>
     </row>
     <row r="16">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>-4.292817286641698</v>
+        <v>-4.292817286641699</v>
       </c>
       <c r="D16">
-        <v>-0.8918882627966889</v>
+        <v>-0.8918882627966895</v>
       </c>
       <c r="E16">
-        <v>0.6235051244205344</v>
+        <v>0.6235051244205919</v>
       </c>
       <c r="F16">
-        <v>2.175967933684576</v>
+        <v>2.175967933684558</v>
       </c>
       <c r="G16">
         <v>0.237584609153268</v>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>3.292939021768931</v>
+        <v>3.292939021768932</v>
       </c>
       <c r="D17">
-        <v>1.458907129677811</v>
+        <v>1.458907129677812</v>
       </c>
       <c r="E17">
-        <v>-0.1899142654331704</v>
+        <v>-0.1899142654331667</v>
       </c>
       <c r="F17">
-        <v>0.1503481835235516</v>
+        <v>0.1503481835235534</v>
       </c>
       <c r="G17">
-        <v>-0.9516828844432965</v>
+        <v>-0.9516828844432991</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>2.410314574922348</v>
+        <v>2.41031457492235</v>
       </c>
       <c r="D18">
-        <v>-2.543746889772548</v>
+        <v>-2.543746889772549</v>
       </c>
       <c r="E18">
-        <v>-0.7310731011095287</v>
+        <v>-0.7310731011095288</v>
       </c>
       <c r="F18">
-        <v>0.00485794603149173</v>
+        <v>0.004857946031512933</v>
       </c>
       <c r="G18">
-        <v>1.454486233235535</v>
+        <v>1.454486233235536</v>
       </c>
     </row>
     <row r="19">
@@ -865,16 +865,16 @@
         <v>1.242949250400653</v>
       </c>
       <c r="D19">
-        <v>-0.9083677007886246</v>
+        <v>-0.9083677007886253</v>
       </c>
       <c r="E19">
-        <v>-1.332658921297156</v>
+        <v>-1.332658921297151</v>
       </c>
       <c r="F19">
-        <v>0.188803480349513</v>
+        <v>0.1888034803495477</v>
       </c>
       <c r="G19">
-        <v>-0.05412154619216752</v>
+        <v>-0.05412154619216766</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>1.403172924880009</v>
+        <v>1.40317292488001</v>
       </c>
       <c r="D20">
-        <v>-1.581439038347874</v>
+        <v>-1.581439038347875</v>
       </c>
       <c r="E20">
-        <v>-0.4741963343576711</v>
+        <v>-0.4741963343576898</v>
       </c>
       <c r="F20">
-        <v>-0.6982110423468565</v>
+        <v>-0.6982110423468431</v>
       </c>
       <c r="G20">
-        <v>0.4193672780737503</v>
+        <v>0.4193672780737509</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.1289661428978733</v>
+        <v>-0.1289661428978731</v>
       </c>
       <c r="D21">
-        <v>0.2704466864552541</v>
+        <v>0.2704466864552545</v>
       </c>
       <c r="E21">
-        <v>2.146964602826503</v>
+        <v>2.146964602826501</v>
       </c>
       <c r="F21">
-        <v>-0.05730895910209555</v>
+        <v>-0.05730895910215397</v>
       </c>
       <c r="G21">
         <v>-1.451688697155</v>
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.2686906830110418</v>
+        <v>0.2686906830110402</v>
       </c>
       <c r="D22">
-        <v>4.321754978889792</v>
+        <v>4.321754978889796</v>
       </c>
       <c r="E22">
-        <v>4.04244132742316</v>
+        <v>4.042441327423195</v>
       </c>
       <c r="F22">
-        <v>1.366867941716624</v>
+        <v>1.366867941716513</v>
       </c>
       <c r="G22">
-        <v>-0.4561401553715937</v>
+        <v>-0.456140155371595</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>2.398172437483279</v>
+        <v>2.39817243748328</v>
       </c>
       <c r="D23">
-        <v>-0.8086348975679536</v>
+        <v>-0.8086348975679531</v>
       </c>
       <c r="E23">
-        <v>0.336314391663101</v>
+        <v>0.3363143916631223</v>
       </c>
       <c r="F23">
-        <v>0.8239467095938229</v>
+        <v>0.823946709593814</v>
       </c>
       <c r="G23">
-        <v>0.6706632351725057</v>
+        <v>0.6706632351725066</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-3.276115185623369</v>
+        <v>-3.27611518562337</v>
       </c>
       <c r="D24">
-        <v>1.913584462006513</v>
+        <v>1.913584462006514</v>
       </c>
       <c r="E24">
-        <v>1.84079300930318</v>
+        <v>1.840793009303219</v>
       </c>
       <c r="F24">
-        <v>1.497072929502051</v>
+        <v>1.497072929502001</v>
       </c>
       <c r="G24">
-        <v>0.5633499926437638</v>
+        <v>0.5633499926437636</v>
       </c>
     </row>
     <row r="25">
@@ -1027,16 +1027,16 @@
         <v>4.113876156197155</v>
       </c>
       <c r="D25">
-        <v>2.031146957055517</v>
+        <v>2.031146957055518</v>
       </c>
       <c r="E25">
-        <v>1.370210204334303</v>
+        <v>1.370210204334226</v>
       </c>
       <c r="F25">
-        <v>-2.854002425918528</v>
+        <v>-2.854002425918565</v>
       </c>
       <c r="G25">
-        <v>0.7870067220956</v>
+        <v>0.7870067220956007</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-5.528922214609145</v>
+        <v>-5.528922214609147</v>
       </c>
       <c r="D26">
-        <v>-0.1456337426930524</v>
+        <v>-0.1456337426930535</v>
       </c>
       <c r="E26">
-        <v>-0.4935119669464288</v>
+        <v>-0.4935119669463898</v>
       </c>
       <c r="F26">
-        <v>1.523884769894578</v>
+        <v>1.523884769894587</v>
       </c>
       <c r="G26">
-        <v>-2.644606293349801</v>
+        <v>-2.644606293349802</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>1.92473156336845</v>
+        <v>1.924731563368451</v>
       </c>
       <c r="D27">
-        <v>3.046704907692295</v>
+        <v>3.046704907692297</v>
       </c>
       <c r="E27">
-        <v>1.149804948482967</v>
+        <v>1.149804948482984</v>
       </c>
       <c r="F27">
-        <v>0.6659702984006129</v>
+        <v>0.6659702984005794</v>
       </c>
       <c r="G27">
-        <v>-0.8133412305518249</v>
+        <v>-0.8133412305518258</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>4.259220759653901</v>
+        <v>4.259220759653902</v>
       </c>
       <c r="D28">
-        <v>-0.9630317923842132</v>
+        <v>-0.9630317923842122</v>
       </c>
       <c r="E28">
-        <v>-0.8256932877034133</v>
+        <v>-0.8256932877034039</v>
       </c>
       <c r="F28">
-        <v>0.3589152426460746</v>
+        <v>0.3589152426460969</v>
       </c>
       <c r="G28">
-        <v>1.306386691896238</v>
+        <v>1.306386691896237</v>
       </c>
     </row>
     <row r="29">
@@ -1132,16 +1132,16 @@
         </is>
       </c>
       <c r="C29">
-        <v>-4.017977562145739</v>
+        <v>-4.017977562145742</v>
       </c>
       <c r="D29">
-        <v>4.007177339963445</v>
+        <v>4.007177339963446</v>
       </c>
       <c r="E29">
-        <v>1.346639429781322</v>
+        <v>1.34663942978135</v>
       </c>
       <c r="F29">
-        <v>1.122370704882893</v>
+        <v>1.122370704882853</v>
       </c>
       <c r="G29">
         <v>-1.01643475835062</v>
@@ -1162,16 +1162,16 @@
         <v>1.433253659064836</v>
       </c>
       <c r="D30">
-        <v>2.410096854245375</v>
+        <v>2.410096854245376</v>
       </c>
       <c r="E30">
-        <v>-0.0506421465931363</v>
+        <v>-0.05064214659312487</v>
       </c>
       <c r="F30">
-        <v>0.4733924036971736</v>
+        <v>0.4733924036971722</v>
       </c>
       <c r="G30">
-        <v>0.3359962685479618</v>
+        <v>0.3359962685479608</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.4854220800330601</v>
+        <v>0.4854220800330602</v>
       </c>
       <c r="D31">
-        <v>0.07030114511607058</v>
+        <v>0.07030114511607138</v>
       </c>
       <c r="E31">
-        <v>0.0115273533165288</v>
+        <v>0.01152735331654813</v>
       </c>
       <c r="F31">
-        <v>0.7498208996262871</v>
+        <v>0.7498208996262861</v>
       </c>
       <c r="G31">
-        <v>0.8866788041323423</v>
+        <v>0.8866788041323415</v>
       </c>
     </row>
     <row r="32">
@@ -1216,16 +1216,16 @@
         <v>1.596658870799691</v>
       </c>
       <c r="D32">
-        <v>3.268256394419054</v>
+        <v>3.268256394419055</v>
       </c>
       <c r="E32">
-        <v>-1.180658103412088</v>
+        <v>-1.180658103412112</v>
       </c>
       <c r="F32">
-        <v>-0.8840745007165258</v>
+        <v>-0.8840745007164976</v>
       </c>
       <c r="G32">
-        <v>0.6197564641558254</v>
+        <v>0.6197564641558246</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1243,16 @@
         <v>-4.424744070662588</v>
       </c>
       <c r="D33">
-        <v>-2.267292135378688</v>
+        <v>-2.267292135378691</v>
       </c>
       <c r="E33">
-        <v>-0.4213702455276546</v>
+        <v>-0.4213702455277175</v>
       </c>
       <c r="F33">
-        <v>-2.349380259400294</v>
+        <v>-2.349380259400284</v>
       </c>
       <c r="G33">
-        <v>-1.859009850703099</v>
+        <v>-1.859009850703101</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>4.917164441593868</v>
+        <v>4.91716444159387</v>
       </c>
       <c r="D34">
         <v>-1.651292476201848</v>
       </c>
       <c r="E34">
-        <v>1.264805085979627</v>
+        <v>1.264805085979617</v>
       </c>
       <c r="F34">
-        <v>-0.3447601749581828</v>
+        <v>-0.3447601749582145</v>
       </c>
       <c r="G34">
-        <v>-0.111578456408463</v>
+        <v>-0.111578456408461</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.1629082988196734</v>
+        <v>0.1629082988196737</v>
       </c>
       <c r="D35">
-        <v>-1.969224859815304</v>
+        <v>-1.969224859815305</v>
       </c>
       <c r="E35">
-        <v>-1.776100697472938</v>
+        <v>-1.776100697472929</v>
       </c>
       <c r="F35">
-        <v>0.4086901992931658</v>
+        <v>0.4086901992932132</v>
       </c>
       <c r="G35">
-        <v>0.259969826820072</v>
+        <v>0.2599698268200735</v>
       </c>
     </row>
     <row r="36">
@@ -1327,13 +1327,13 @@
         <v>-2.027751969888615</v>
       </c>
       <c r="E36">
-        <v>0.5705511604986206</v>
+        <v>0.5705511604986364</v>
       </c>
       <c r="F36">
-        <v>0.606109181736857</v>
+        <v>0.6061091817368416</v>
       </c>
       <c r="G36">
-        <v>-0.1731761402853765</v>
+        <v>-0.1731761402853774</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-4.667902573532464</v>
+        <v>-4.667902573532463</v>
       </c>
       <c r="D37">
-        <v>-2.781283234403861</v>
+        <v>-2.781283234403864</v>
       </c>
       <c r="E37">
-        <v>-2.069281304691895</v>
+        <v>-2.069281304691872</v>
       </c>
       <c r="F37">
-        <v>0.8086886849713472</v>
+        <v>0.8086886849714016</v>
       </c>
       <c r="G37">
-        <v>0.7818262358655814</v>
+        <v>0.7818262358655806</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.4096707574060945</v>
+        <v>-0.4096707574060942</v>
       </c>
       <c r="D38">
-        <v>-1.288132922658258</v>
+        <v>-1.288132922658259</v>
       </c>
       <c r="E38">
-        <v>-1.834799282102823</v>
+        <v>-1.834799282102817</v>
       </c>
       <c r="F38">
-        <v>0.2381234526350611</v>
+        <v>0.2381234526351111</v>
       </c>
       <c r="G38">
-        <v>2.625720444609702</v>
+        <v>2.625720444609703</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.4266015886596934</v>
+        <v>0.4266015886596937</v>
       </c>
       <c r="D39">
         <v>0.9778548431774959</v>
       </c>
       <c r="E39">
-        <v>0.2820657695251922</v>
+        <v>0.2820657695251797</v>
       </c>
       <c r="F39">
-        <v>-0.4525907522230744</v>
+        <v>-0.4525907522230831</v>
       </c>
       <c r="G39">
-        <v>0.05127031978453903</v>
+        <v>0.05127031978453893</v>
       </c>
     </row>
     <row r="40">
@@ -1432,16 +1432,16 @@
         <v>2.475471132281606</v>
       </c>
       <c r="D40">
-        <v>2.376399044131663</v>
+        <v>2.376399044131665</v>
       </c>
       <c r="E40">
-        <v>-1.773943410676296</v>
+        <v>-1.773943410676312</v>
       </c>
       <c r="F40">
-        <v>-0.5807969619494441</v>
+        <v>-0.5807969619494009</v>
       </c>
       <c r="G40">
-        <v>-0.9421013133715024</v>
+        <v>-0.9421013133715028</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.590803940860726</v>
+        <v>0.5908039408607256</v>
       </c>
       <c r="D41">
-        <v>2.323655898647419</v>
+        <v>2.323655898647421</v>
       </c>
       <c r="E41">
-        <v>2.279567881043948</v>
+        <v>2.279567881043968</v>
       </c>
       <c r="F41">
-        <v>0.8206542134757604</v>
+        <v>0.8206542134756983</v>
       </c>
       <c r="G41">
-        <v>0.5965035044847349</v>
+        <v>0.5965035044847345</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>2.950653071481627</v>
+        <v>2.950653071481629</v>
       </c>
       <c r="D42">
         <v>-2.170279546537264</v>
       </c>
       <c r="E42">
-        <v>-1.214527357160159</v>
+        <v>-1.214527357160149</v>
       </c>
       <c r="F42">
-        <v>0.364179953234631</v>
+        <v>0.364179953234664</v>
       </c>
       <c r="G42">
-        <v>0.7848916287012856</v>
+        <v>0.784891628701285</v>
       </c>
     </row>
     <row r="43">
@@ -1513,16 +1513,16 @@
         <v>-6.47919097483534</v>
       </c>
       <c r="D43">
-        <v>2.154866605288831</v>
+        <v>2.154866605288829</v>
       </c>
       <c r="E43">
-        <v>-1.817250554451805</v>
+        <v>-1.81725055445182</v>
       </c>
       <c r="F43">
-        <v>-0.5617075131868203</v>
+        <v>-0.5617075131867784</v>
       </c>
       <c r="G43">
-        <v>-2.832076358810661</v>
+        <v>-2.832076358810662</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>2.287408448830478</v>
+        <v>2.287408448830479</v>
       </c>
       <c r="D44">
         <v>-2.457423136891328</v>
       </c>
       <c r="E44">
-        <v>0.9893903965224817</v>
+        <v>0.9893903965224968</v>
       </c>
       <c r="F44">
-        <v>0.5864693283168532</v>
+        <v>0.5864693283168283</v>
       </c>
       <c r="G44">
-        <v>-0.4379257304566435</v>
+        <v>-0.437925730456643</v>
       </c>
     </row>
     <row r="45">
@@ -1570,13 +1570,13 @@
         <v>1.875720248072952</v>
       </c>
       <c r="E45">
-        <v>-1.104088177586726</v>
+        <v>-1.104088177586746</v>
       </c>
       <c r="F45">
-        <v>-0.703798537841856</v>
+        <v>-0.7037985378418303</v>
       </c>
       <c r="G45">
-        <v>-1.156526069590397</v>
+        <v>-1.156526069590398</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-4.716575900164393</v>
+        <v>-4.716575900164394</v>
       </c>
       <c r="D46">
-        <v>-0.903118044180186</v>
+        <v>-0.9031180441801855</v>
       </c>
       <c r="E46">
-        <v>0.6888318787839288</v>
+        <v>0.6888318787839602</v>
       </c>
       <c r="F46">
-        <v>1.211226604827259</v>
+        <v>1.21122660482724</v>
       </c>
       <c r="G46">
-        <v>-0.1308368878242655</v>
+        <v>-0.1308368878242647</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>3.994751297689532</v>
+        <v>3.994751297689533</v>
       </c>
       <c r="D47">
-        <v>-0.4621876423714251</v>
+        <v>-0.4621876423714246</v>
       </c>
       <c r="E47">
-        <v>0.7332659555411642</v>
+        <v>0.7332659555411449</v>
       </c>
       <c r="F47">
-        <v>-0.7027118329466208</v>
+        <v>-0.7027118329466404</v>
       </c>
       <c r="G47">
-        <v>-0.728723406950291</v>
+        <v>-0.7287234069502911</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>6.687454227331092</v>
+        <v>6.687454227331093</v>
       </c>
       <c r="D48">
-        <v>0.04723619455174136</v>
+        <v>0.04723619455174197</v>
       </c>
       <c r="E48">
-        <v>-0.3853863161985098</v>
+        <v>-0.3853863161985378</v>
       </c>
       <c r="F48">
-        <v>-1.018956389218504</v>
+        <v>-1.018956389218494</v>
       </c>
       <c r="G48">
-        <v>0.03311257984051024</v>
+        <v>0.03311257984050942</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>2.732462993541609</v>
+        <v>2.732462993541611</v>
       </c>
       <c r="D49">
         <v>1.990732292423777</v>
       </c>
       <c r="E49">
-        <v>-1.111551102728643</v>
+        <v>-1.111551102728684</v>
       </c>
       <c r="F49">
-        <v>-1.499388572530235</v>
+        <v>-1.499388572530208</v>
       </c>
       <c r="G49">
-        <v>-0.2323390748264927</v>
+        <v>-0.2323390748264935</v>
       </c>
     </row>
     <row r="50">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.1395405892638966</v>
+        <v>-0.1395405892638965</v>
       </c>
       <c r="D50">
-        <v>-0.5406335249942108</v>
+        <v>-0.5406335249942115</v>
       </c>
       <c r="E50">
-        <v>0.2222119490461889</v>
+        <v>0.2222119490461795</v>
       </c>
       <c r="F50">
-        <v>-0.3327088328201089</v>
+        <v>-0.3327088328201159</v>
       </c>
       <c r="G50">
         <v>-1.320272397175238</v>
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>5.340184314125738</v>
+        <v>5.340184314125739</v>
       </c>
       <c r="D51">
-        <v>0.6229608406068239</v>
+        <v>0.622960840606825</v>
       </c>
       <c r="E51">
-        <v>-0.999658403804181</v>
+        <v>-0.9996584038041932</v>
       </c>
       <c r="F51">
-        <v>-0.4305739119259961</v>
+        <v>-0.4305739119259708</v>
       </c>
       <c r="G51">
-        <v>-0.1511656478561679</v>
+        <v>-0.1511656478561686</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>3.274246933618091</v>
+        <v>3.274246933618093</v>
       </c>
       <c r="D52">
-        <v>-0.5350036437913114</v>
+        <v>-0.5350036437913108</v>
       </c>
       <c r="E52">
-        <v>-1.860297997973005</v>
+        <v>-1.860297997973004</v>
       </c>
       <c r="F52">
-        <v>0.01875121587468316</v>
+        <v>0.01875121587473164</v>
       </c>
       <c r="G52">
-        <v>0.2603927621905102</v>
+        <v>0.2603927621905087</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>1.397345871994116</v>
+        <v>1.397345871994117</v>
       </c>
       <c r="D53">
         <v>-1.633803514881338</v>
       </c>
       <c r="E53">
-        <v>0.720826411653598</v>
+        <v>0.7208264116536205</v>
       </c>
       <c r="F53">
-        <v>0.8677814245875347</v>
+        <v>0.8677814245875162</v>
       </c>
       <c r="G53">
-        <v>-0.1364574845901976</v>
+        <v>-0.1364574845901977</v>
       </c>
     </row>
     <row r="54">
@@ -1810,16 +1810,16 @@
         <v>-2.27445899900286</v>
       </c>
       <c r="D54">
-        <v>-2.209018053981939</v>
+        <v>-2.20901805398194</v>
       </c>
       <c r="E54">
-        <v>-0.04323487596988819</v>
+        <v>-0.04323487596983083</v>
       </c>
       <c r="F54">
         <v>2.164419582572993</v>
       </c>
       <c r="G54">
-        <v>0.8856365642978075</v>
+        <v>0.8856365642978077</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-1.064909374742896</v>
+        <v>-1.064909374742897</v>
       </c>
       <c r="D55">
-        <v>0.6974390899711316</v>
+        <v>0.6974390899711324</v>
       </c>
       <c r="E55">
-        <v>1.649251606820271</v>
+        <v>1.649251606820301</v>
       </c>
       <c r="F55">
-        <v>1.153023670607201</v>
+        <v>1.153023670607157</v>
       </c>
       <c r="G55">
-        <v>0.917982758515133</v>
+        <v>0.917982758515134</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>2.847689682117244</v>
+        <v>2.847689682117245</v>
       </c>
       <c r="D56">
-        <v>-0.5974615478654599</v>
+        <v>-0.5974615478654602</v>
       </c>
       <c r="E56">
-        <v>1.913680098742082</v>
+        <v>1.913680098742046</v>
       </c>
       <c r="F56">
-        <v>-1.293994395031727</v>
+        <v>-1.293994395031778</v>
       </c>
       <c r="G56">
-        <v>-1.72519257858883</v>
+        <v>-1.725192578588829</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>2.328221425618852</v>
+        <v>2.328221425618853</v>
       </c>
       <c r="D57">
-        <v>-0.2920460473230819</v>
+        <v>-0.2920460473230818</v>
       </c>
       <c r="E57">
-        <v>1.050577442495448</v>
+        <v>1.050577442495426</v>
       </c>
       <c r="F57">
-        <v>-0.8311718934102702</v>
+        <v>-0.8311718934102978</v>
       </c>
       <c r="G57">
-        <v>-0.1327526164483369</v>
+        <v>-0.132752616448336</v>
       </c>
     </row>
     <row r="58">
@@ -1915,16 +1915,16 @@
         </is>
       </c>
       <c r="C58">
-        <v>3.912121557756061</v>
+        <v>3.912121557756062</v>
       </c>
       <c r="D58">
-        <v>1.324068539198393</v>
+        <v>1.324068539198395</v>
       </c>
       <c r="E58">
-        <v>-0.4611819504953246</v>
+        <v>-0.4611819504953541</v>
       </c>
       <c r="F58">
-        <v>-1.082976632761975</v>
+        <v>-1.082976632761963</v>
       </c>
       <c r="G58">
         <v>1.636971071157555</v>
@@ -1942,16 +1942,16 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.4210930319584553</v>
+        <v>0.4210930319584552</v>
       </c>
       <c r="D59">
-        <v>1.231724722387284</v>
+        <v>1.231724722387286</v>
       </c>
       <c r="E59">
-        <v>0.7029365239879334</v>
+        <v>0.7029365239879504</v>
       </c>
       <c r="F59">
-        <v>0.6515547913030698</v>
+        <v>0.6515547913030513</v>
       </c>
       <c r="G59">
         <v>2.360478387561888</v>
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>3.407460738406215</v>
+        <v>3.407460738406218</v>
       </c>
       <c r="D60">
         <v>-2.22007152106634</v>
       </c>
       <c r="E60">
-        <v>-0.1239252298528912</v>
+        <v>-0.1239252298529173</v>
       </c>
       <c r="F60">
-        <v>-0.9530756623534296</v>
+        <v>-0.9530756623534258</v>
       </c>
       <c r="G60">
-        <v>-0.324438721135293</v>
+        <v>-0.3244387211352924</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-3.618057753434717</v>
+        <v>-3.618057753434718</v>
       </c>
       <c r="D61">
-        <v>0.7789033855485977</v>
+        <v>0.7789033855485979</v>
       </c>
       <c r="E61">
-        <v>-0.4539420941857897</v>
+        <v>-0.4539420941857578</v>
       </c>
       <c r="F61">
-        <v>1.206971394071165</v>
+        <v>1.206971394071173</v>
       </c>
       <c r="G61">
-        <v>-0.2587890471356135</v>
+        <v>-0.2587890471356156</v>
       </c>
     </row>
     <row r="62">
@@ -2026,16 +2026,16 @@
         <v>2.493525389554841</v>
       </c>
       <c r="D62">
-        <v>0.415625651708334</v>
+        <v>0.4156256517083347</v>
       </c>
       <c r="E62">
-        <v>0.5755171277235245</v>
+        <v>0.5755171277235047</v>
       </c>
       <c r="F62">
-        <v>-0.7125213582472281</v>
+        <v>-0.7125213582472458</v>
       </c>
       <c r="G62">
-        <v>-1.781320814768143</v>
+        <v>-1.781320814768145</v>
       </c>
     </row>
     <row r="63">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="C63">
-        <v>4.334853618087457</v>
+        <v>4.334853618087458</v>
       </c>
       <c r="D63">
         <v>1.658611628330263</v>
       </c>
       <c r="E63">
-        <v>0.1329695115949043</v>
+        <v>0.132969511594885</v>
       </c>
       <c r="F63">
-        <v>-0.6996488793217031</v>
+        <v>-0.6996488793217079</v>
       </c>
       <c r="G63">
         <v>0.3516645978947527</v>
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>5.5625279679992</v>
+        <v>5.562527967999203</v>
       </c>
       <c r="D64">
         <v>-1.016064108509041</v>
       </c>
       <c r="E64">
-        <v>-0.2581056915076101</v>
+        <v>-0.2581056915076294</v>
       </c>
       <c r="F64">
-        <v>-0.7003895593257355</v>
+        <v>-0.7003895593257272</v>
       </c>
       <c r="G64">
-        <v>0.7344505326776926</v>
+        <v>0.7344505326776924</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>3.210560005653203</v>
+        <v>3.210560005653205</v>
       </c>
       <c r="D65">
-        <v>-3.608171803472807</v>
+        <v>-3.608171803472808</v>
       </c>
       <c r="E65">
-        <v>-0.03070796777685431</v>
+        <v>-0.03070796777685886</v>
       </c>
       <c r="F65">
-        <v>-0.144780146619551</v>
+        <v>-0.1447801466195482</v>
       </c>
       <c r="G65">
-        <v>-0.01732333620723865</v>
+        <v>-0.01732333620723792</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>-2.94624937892849</v>
+        <v>-2.946249378928491</v>
       </c>
       <c r="D66">
-        <v>1.391319292773636</v>
+        <v>1.391319292773635</v>
       </c>
       <c r="E66">
-        <v>-2.791188146796808</v>
+        <v>-2.791188146796801</v>
       </c>
       <c r="F66">
-        <v>0.2795303489477168</v>
+        <v>0.2795303489477883</v>
       </c>
       <c r="G66">
-        <v>0.3877604256837418</v>
+        <v>0.3877604256837424</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>1.589371061447238</v>
+        <v>1.589371061447239</v>
       </c>
       <c r="D67">
-        <v>-0.7940826923204813</v>
+        <v>-0.7940826923204816</v>
       </c>
       <c r="E67">
-        <v>-0.09497263085003507</v>
+        <v>-0.09497263085002769</v>
       </c>
       <c r="F67">
-        <v>0.3221905823433326</v>
+        <v>0.3221905823433346</v>
       </c>
       <c r="G67">
-        <v>-0.7152173606053387</v>
+        <v>-0.7152173606053384</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>1.557899393027625</v>
+        <v>1.557899393027626</v>
       </c>
       <c r="D68">
-        <v>0.3151527361020917</v>
+        <v>0.3151527361020906</v>
       </c>
       <c r="E68">
-        <v>-2.630400266601876</v>
+        <v>-2.630400266601919</v>
       </c>
       <c r="F68">
-        <v>-1.651088853695899</v>
+        <v>-1.65108885369583</v>
       </c>
       <c r="G68">
-        <v>1.653020001851086</v>
+        <v>1.653020001851087</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>-1.675073112988196</v>
+        <v>-1.675073112988197</v>
       </c>
       <c r="D69">
-        <v>0.2756294531809506</v>
+        <v>0.2756294531809514</v>
       </c>
       <c r="E69">
-        <v>2.659100265506788</v>
+        <v>2.659100265506799</v>
       </c>
       <c r="F69">
-        <v>0.4427204083584724</v>
+        <v>0.4427204083584012</v>
       </c>
       <c r="G69">
-        <v>0.3348615900549393</v>
+        <v>0.3348615900549388</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>3.575522183381199</v>
+        <v>3.575522183381201</v>
       </c>
       <c r="D70">
         <v>-1.42649107701184</v>
       </c>
       <c r="E70">
-        <v>1.202318355415846</v>
+        <v>1.202318355415847</v>
       </c>
       <c r="F70">
-        <v>0.0755782526164904</v>
+        <v>0.07557825261645873</v>
       </c>
       <c r="G70">
-        <v>-0.6120183228082843</v>
+        <v>-0.6120183228082847</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>1.640638725174715</v>
+        <v>1.640638725174716</v>
       </c>
       <c r="D71">
-        <v>1.012884781636587</v>
+        <v>1.012884781636588</v>
       </c>
       <c r="E71">
-        <v>-2.193555972321284</v>
+        <v>-2.193555972321264</v>
       </c>
       <c r="F71">
-        <v>0.7740250383048521</v>
+        <v>0.774025038304908</v>
       </c>
       <c r="G71">
-        <v>0.09817869898117582</v>
+        <v>0.09817869898117512</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-10.68945466831981</v>
+        <v>-10.68945466831982</v>
       </c>
       <c r="D72">
-        <v>2.048113621887692</v>
+        <v>2.048113621887687</v>
       </c>
       <c r="E72">
-        <v>2.006937736079355</v>
+        <v>2.006937736079222</v>
       </c>
       <c r="F72">
-        <v>-4.950547235726036</v>
+        <v>-4.950547235726091</v>
       </c>
       <c r="G72">
-        <v>1.584253233116388</v>
+        <v>1.58425323311639</v>
       </c>
     </row>
     <row r="73">
@@ -2323,16 +2323,16 @@
         <v>-3.320111047482329</v>
       </c>
       <c r="D73">
-        <v>-1.448038608722063</v>
+        <v>-1.448038608722065</v>
       </c>
       <c r="E73">
-        <v>0.6462420391836774</v>
+        <v>0.6462420391836902</v>
       </c>
       <c r="F73">
-        <v>0.5567851087121177</v>
+        <v>0.5567851087121002</v>
       </c>
       <c r="G73">
-        <v>-0.6329171365364329</v>
+        <v>-0.6329171365364317</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>-4.130523486125571</v>
+        <v>-4.130523486125573</v>
       </c>
       <c r="D74">
-        <v>-0.1114720687515279</v>
+        <v>-0.1114720687515284</v>
       </c>
       <c r="E74">
-        <v>0.45048926721163</v>
+        <v>0.4504892672116712</v>
       </c>
       <c r="F74">
-        <v>1.567620533166247</v>
+        <v>1.567620533166234</v>
       </c>
       <c r="G74">
-        <v>0.7403204175550133</v>
+        <v>0.7403204175550131</v>
       </c>
     </row>
     <row r="75">
@@ -2377,16 +2377,16 @@
         <v>-3.936206664357037</v>
       </c>
       <c r="D75">
-        <v>-1.064952814384237</v>
+        <v>-1.064952814384241</v>
       </c>
       <c r="E75">
-        <v>0.6277928038879063</v>
+        <v>0.6277928038878331</v>
       </c>
       <c r="F75">
-        <v>-2.730827299080698</v>
+        <v>-2.730827299080716</v>
       </c>
       <c r="G75">
-        <v>-0.932018725152833</v>
+        <v>-0.932018725152832</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-7.498793515849651</v>
+        <v>-7.498793515849654</v>
       </c>
       <c r="D76">
-        <v>1.573608963638889</v>
+        <v>1.57360896363889</v>
       </c>
       <c r="E76">
-        <v>2.156933697440731</v>
+        <v>2.156933697440749</v>
       </c>
       <c r="F76">
-        <v>0.7247340925423327</v>
+        <v>0.7247340925422732</v>
       </c>
       <c r="G76">
-        <v>-0.2619795448327047</v>
+        <v>-0.2619795448327049</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>2.350334193974969</v>
+        <v>2.350334193974971</v>
       </c>
       <c r="D77">
-        <v>-2.1773464337089</v>
+        <v>-2.177346433708902</v>
       </c>
       <c r="E77">
-        <v>1.660042090841614</v>
+        <v>1.660042090841588</v>
       </c>
       <c r="F77">
-        <v>-0.9416839678512681</v>
+        <v>-0.9416839678513108</v>
       </c>
       <c r="G77">
-        <v>-0.8556582444801689</v>
+        <v>-0.8556582444801683</v>
       </c>
     </row>
     <row r="78">
@@ -2458,16 +2458,16 @@
         <v>2.89571496565968</v>
       </c>
       <c r="D78">
-        <v>0.7646672958984541</v>
+        <v>0.7646672958984561</v>
       </c>
       <c r="E78">
-        <v>0.5088014091818265</v>
+        <v>0.5088014091818739</v>
       </c>
       <c r="F78">
-        <v>1.825922385050605</v>
+        <v>1.82592238505059</v>
       </c>
       <c r="G78">
-        <v>-0.009714221132745402</v>
+        <v>-0.009714221132745532</v>
       </c>
     </row>
     <row r="79">
@@ -2488,13 +2488,13 @@
         <v>1.693701145472034</v>
       </c>
       <c r="E79">
-        <v>-2.956479028429099</v>
+        <v>-2.956479028429073</v>
       </c>
       <c r="F79">
-        <v>0.9855549102924306</v>
+        <v>0.9855549102925041</v>
       </c>
       <c r="G79">
-        <v>-1.41480590623412</v>
+        <v>-1.414805906234121</v>
       </c>
     </row>
     <row r="80">
@@ -2512,16 +2512,16 @@
         <v>1.483933812146157</v>
       </c>
       <c r="D80">
-        <v>3.110018932150854</v>
+        <v>3.110018932150855</v>
       </c>
       <c r="E80">
-        <v>-0.3007490674475369</v>
+        <v>-0.3007490674475412</v>
       </c>
       <c r="F80">
-        <v>-0.130125058811809</v>
+        <v>-0.1301250588118036</v>
       </c>
       <c r="G80">
-        <v>0.8712852987190255</v>
+        <v>0.8712852987190249</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-2.455481236815556</v>
+        <v>-2.455481236815557</v>
       </c>
       <c r="D81">
-        <v>-0.1423486259688877</v>
+        <v>-0.1423486259688889</v>
       </c>
       <c r="E81">
-        <v>-1.511546424068345</v>
+        <v>-1.511546424068324</v>
       </c>
       <c r="F81">
-        <v>0.7838626248028515</v>
+        <v>0.7838626248028885</v>
       </c>
       <c r="G81">
-        <v>-1.198560697796161</v>
+        <v>-1.198560697796163</v>
       </c>
     </row>
     <row r="82">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.4716995353729249</v>
+        <v>-0.4716995353729246</v>
       </c>
       <c r="D82">
-        <v>-1.79253012476981</v>
+        <v>-1.792530124769812</v>
       </c>
       <c r="E82">
         <v>-1.046022452164339</v>
       </c>
       <c r="F82">
-        <v>0.01371994879711716</v>
+        <v>0.01371994879714517</v>
       </c>
       <c r="G82">
         <v>1.144245597624822</v>
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.3361813078198696</v>
+        <v>-0.3361813078198692</v>
       </c>
       <c r="D83">
-        <v>-1.097454750413405</v>
+        <v>-1.097454750413406</v>
       </c>
       <c r="E83">
-        <v>1.76576580062705</v>
+        <v>1.765765800627043</v>
       </c>
       <c r="F83">
-        <v>-0.2353756700538562</v>
+        <v>-0.2353756700539041</v>
       </c>
       <c r="G83">
-        <v>-1.196675708230633</v>
+        <v>-1.196675708230634</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>2.87964754377396</v>
+        <v>2.879647543773961</v>
       </c>
       <c r="D84">
-        <v>2.084298945951941</v>
+        <v>2.084298945951944</v>
       </c>
       <c r="E84">
-        <v>1.448218620979824</v>
+        <v>1.448218620979805</v>
       </c>
       <c r="F84">
-        <v>-0.6545539184450412</v>
+        <v>-0.6545539184450815</v>
       </c>
       <c r="G84">
-        <v>0.1015128627185544</v>
+        <v>0.1015128627185542</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>6.276050423349166</v>
+        <v>6.276050423349169</v>
       </c>
       <c r="D85">
-        <v>0.8617956388907725</v>
+        <v>0.8617956388907728</v>
       </c>
       <c r="E85">
-        <v>0.07143489213403721</v>
+        <v>0.07143489213398463</v>
       </c>
       <c r="F85">
-        <v>-1.923135482507685</v>
+        <v>-1.923135482507688</v>
       </c>
       <c r="G85">
-        <v>-0.249875238399541</v>
+        <v>-0.2498752383995412</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>4.787954224406307</v>
+        <v>4.787954224406309</v>
       </c>
       <c r="D86">
-        <v>1.081145669725764</v>
+        <v>1.081145669725765</v>
       </c>
       <c r="E86">
-        <v>0.1418155930294532</v>
+        <v>0.1418155930294095</v>
       </c>
       <c r="F86">
-        <v>-1.599611022550333</v>
+        <v>-1.599611022550337</v>
       </c>
       <c r="G86">
-        <v>-0.06128412792825664</v>
+        <v>-0.06128412792825735</v>
       </c>
     </row>
     <row r="87">
@@ -2701,16 +2701,16 @@
         <v>-1.639293074578072</v>
       </c>
       <c r="D87">
-        <v>-0.6222635038841832</v>
+        <v>-0.6222635038841849</v>
       </c>
       <c r="E87">
-        <v>-1.640623629546828</v>
+        <v>-1.640623629546834</v>
       </c>
       <c r="F87">
-        <v>-0.2581094924077246</v>
+        <v>-0.258109492407683</v>
       </c>
       <c r="G87">
-        <v>-0.7472641811476407</v>
+        <v>-0.7472641811476411</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>6.703200406785613</v>
+        <v>6.703200406785616</v>
       </c>
       <c r="D88">
         <v>-0.6064562054996566</v>
       </c>
       <c r="E88">
-        <v>-0.08736569718589762</v>
+        <v>-0.08736569718592953</v>
       </c>
       <c r="F88">
-        <v>-1.161097281115011</v>
+        <v>-1.161097281115008</v>
       </c>
       <c r="G88">
-        <v>0.3884208393230854</v>
+        <v>0.3884208393230874</v>
       </c>
     </row>
     <row r="89">
@@ -2755,16 +2755,16 @@
         <v>2.840511015231958</v>
       </c>
       <c r="D89">
-        <v>1.058992352482842</v>
+        <v>1.058992352482843</v>
       </c>
       <c r="E89">
-        <v>1.284796216691684</v>
+        <v>1.28479621669168</v>
       </c>
       <c r="F89">
-        <v>-0.1323621532762163</v>
+        <v>-0.132362153276251</v>
       </c>
       <c r="G89">
-        <v>0.6233769601802395</v>
+        <v>0.6233769601802389</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-2.150406454214996</v>
+        <v>-2.150406454214997</v>
       </c>
       <c r="D90">
-        <v>1.863473656232936</v>
+        <v>1.863473656232937</v>
       </c>
       <c r="E90">
-        <v>-0.5973061977834864</v>
+        <v>-0.5973061977834551</v>
       </c>
       <c r="F90">
-        <v>1.201114338502137</v>
+        <v>1.20111433850215</v>
       </c>
       <c r="G90">
-        <v>0.8136893394102385</v>
+        <v>0.8136893394102387</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>-2.691627050387671</v>
+        <v>-2.691627050387673</v>
       </c>
       <c r="D91">
         <v>-1.967791621101488</v>
       </c>
       <c r="E91">
-        <v>-0.9950021128853821</v>
+        <v>-0.9950021128853412</v>
       </c>
       <c r="F91">
-        <v>1.549072020077221</v>
+        <v>1.549072020077247</v>
       </c>
       <c r="G91">
-        <v>-0.292788830822298</v>
+        <v>-0.2927888308222988</v>
       </c>
     </row>
     <row r="92">
@@ -2839,13 +2839,13 @@
         <v>2.831331408677314</v>
       </c>
       <c r="E92">
-        <v>-0.5872555753767118</v>
+        <v>-0.5872555753767331</v>
       </c>
       <c r="F92">
-        <v>-0.7774845113647159</v>
+        <v>-0.7774845113647034</v>
       </c>
       <c r="G92">
-        <v>0.3650222282258703</v>
+        <v>0.3650222282258701</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>2.543302402702651</v>
+        <v>2.543302402702652</v>
       </c>
       <c r="D93">
-        <v>-0.9624228747723176</v>
+        <v>-0.9624228747723194</v>
       </c>
       <c r="E93">
-        <v>0.03163373651555359</v>
+        <v>0.03163373651549491</v>
       </c>
       <c r="F93">
-        <v>-2.171886386399882</v>
+        <v>-2.171886386399883</v>
       </c>
       <c r="G93">
-        <v>-0.8125944441424754</v>
+        <v>-0.8125944441424759</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-1.317713066018691</v>
+        <v>-1.317713066018692</v>
       </c>
       <c r="D94">
         <v>2.075647037083021</v>
       </c>
       <c r="E94">
-        <v>-2.209480405011846</v>
+        <v>-2.209480405011815</v>
       </c>
       <c r="F94">
-        <v>1.205914473601281</v>
+        <v>1.205914473601336</v>
       </c>
       <c r="G94">
-        <v>0.5196417662245766</v>
+        <v>0.5196417662245763</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-8.460697984123835</v>
+        <v>-8.460697984123838</v>
       </c>
       <c r="D95">
-        <v>1.281498228202165</v>
+        <v>1.281498228202163</v>
       </c>
       <c r="E95">
-        <v>1.232030313797753</v>
+        <v>1.232030313797745</v>
       </c>
       <c r="F95">
-        <v>-0.2431453169758465</v>
+        <v>-0.2431453169758813</v>
       </c>
       <c r="G95">
-        <v>0.6666769773706963</v>
+        <v>0.6666769773706991</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.7216998801426127</v>
+        <v>-0.7216998801426131</v>
       </c>
       <c r="D96">
-        <v>0.576676158480114</v>
+        <v>0.5766761584801148</v>
       </c>
       <c r="E96">
-        <v>-0.6083664476456355</v>
+        <v>-0.6083664476456075</v>
       </c>
       <c r="F96">
-        <v>1.064299787671906</v>
+        <v>1.064299787671921</v>
       </c>
       <c r="G96">
-        <v>0.705037005032533</v>
+        <v>0.7050370050325325</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>3.122754726341259</v>
+        <v>3.122754726341261</v>
       </c>
       <c r="D97">
-        <v>-2.518833573893703</v>
+        <v>-2.518833573893705</v>
       </c>
       <c r="E97">
-        <v>0.652542938180641</v>
+        <v>0.6525429381805843</v>
       </c>
       <c r="F97">
-        <v>-2.072469336551381</v>
+        <v>-2.072469336551398</v>
       </c>
       <c r="G97">
-        <v>-1.719395980814873</v>
+        <v>-1.719395980814874</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-7.557595216692208</v>
+        <v>-7.557595216692209</v>
       </c>
       <c r="D98">
-        <v>-3.122867328889052</v>
+        <v>-3.122867328889058</v>
       </c>
       <c r="E98">
-        <v>-1.578372871158311</v>
+        <v>-1.578372871158319</v>
       </c>
       <c r="F98">
-        <v>-0.2664351568435251</v>
+        <v>-0.2664351568434821</v>
       </c>
       <c r="G98">
-        <v>1.377510720025933</v>
+        <v>1.377510720025935</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.6511947626242099</v>
+        <v>0.6511947626242107</v>
       </c>
       <c r="D99">
-        <v>-2.244630790117721</v>
+        <v>-2.24463079011772</v>
       </c>
       <c r="E99">
-        <v>0.09468777875374321</v>
+        <v>0.09468777875378143</v>
       </c>
       <c r="F99">
-        <v>1.456862071235709</v>
+        <v>1.456862071235706</v>
       </c>
       <c r="G99">
-        <v>-0.07583705296947459</v>
+        <v>-0.07583705296947474</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>1.801597072477779</v>
+        <v>1.80159707247778</v>
       </c>
       <c r="D100">
         <v>-2.387002384366603</v>
       </c>
       <c r="E100">
-        <v>2.231704002883414</v>
+        <v>2.231704002883434</v>
       </c>
       <c r="F100">
-        <v>0.7612405120252254</v>
+        <v>0.7612405120251678</v>
       </c>
       <c r="G100">
-        <v>-0.3938740126266048</v>
+        <v>-0.393874012626604</v>
       </c>
     </row>
     <row r="101">
@@ -3079,16 +3079,16 @@
         <v>1.341656992233995</v>
       </c>
       <c r="D101">
-        <v>-0.06271325409801051</v>
+        <v>-0.06271325409800876</v>
       </c>
       <c r="E101">
-        <v>2.577064488092346</v>
+        <v>2.577064488092399</v>
       </c>
       <c r="F101">
-        <v>2.014907037732018</v>
+        <v>2.014907037731949</v>
       </c>
       <c r="G101">
-        <v>-1.113611690217977</v>
+        <v>-1.113611690217979</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.1771029374522816</v>
+        <v>0.1771029374522819</v>
       </c>
       <c r="D102">
-        <v>1.249406410032224</v>
+        <v>1.249406410032222</v>
       </c>
       <c r="E102">
-        <v>-2.574549854202262</v>
+        <v>-2.574549854202345</v>
       </c>
       <c r="F102">
-        <v>-3.118089943628032</v>
+        <v>-3.118089943627967</v>
       </c>
       <c r="G102">
-        <v>-1.323237519614611</v>
+        <v>-1.323237519614612</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>2.539066193697078</v>
+        <v>2.539066193697079</v>
       </c>
       <c r="D103">
-        <v>0.4152128652799403</v>
+        <v>0.4152128652799416</v>
       </c>
       <c r="E103">
         <v>1.067666414614405</v>
       </c>
       <c r="F103">
-        <v>0.0256171074234345</v>
+        <v>0.02561710742340513</v>
       </c>
       <c r="G103">
-        <v>-0.7813936555540216</v>
+        <v>-0.7813936555540226</v>
       </c>
     </row>
     <row r="104">
@@ -3157,16 +3157,16 @@
         </is>
       </c>
       <c r="C104">
-        <v>1.31673738523507</v>
+        <v>1.316737385235071</v>
       </c>
       <c r="D104">
-        <v>-1.452255633795485</v>
+        <v>-1.452255633795484</v>
       </c>
       <c r="E104">
-        <v>2.066340518175234</v>
+        <v>2.06634051817527</v>
       </c>
       <c r="F104">
-        <v>1.359931565174201</v>
+        <v>1.359931565174147</v>
       </c>
       <c r="G104">
         <v>1.257584840781818</v>
@@ -3187,16 +3187,16 @@
         <v>1.723508036217847</v>
       </c>
       <c r="D105">
-        <v>0.8959118279716556</v>
+        <v>0.8959118279716578</v>
       </c>
       <c r="E105">
-        <v>1.21476934990122</v>
+        <v>1.214769349901276</v>
       </c>
       <c r="F105">
-        <v>2.093853869742169</v>
+        <v>2.093853869742134</v>
       </c>
       <c r="G105">
-        <v>-1.339965086114402</v>
+        <v>-1.339965086114405</v>
       </c>
     </row>
     <row r="106">
@@ -3214,16 +3214,16 @@
         <v>-1.576175590572001</v>
       </c>
       <c r="D106">
-        <v>-1.781218534259876</v>
+        <v>-1.781218534259878</v>
       </c>
       <c r="E106">
-        <v>2.779725256187544</v>
+        <v>2.779725256187527</v>
       </c>
       <c r="F106">
-        <v>-0.5791762108488373</v>
+        <v>-0.5791762108489067</v>
       </c>
       <c r="G106">
-        <v>3.612432290716667</v>
+        <v>3.61243229071667</v>
       </c>
     </row>
     <row r="107">
@@ -3241,16 +3241,16 @@
         <v>-2.352163185277147</v>
       </c>
       <c r="D107">
-        <v>0.5765275719151947</v>
+        <v>0.5765275719151939</v>
       </c>
       <c r="E107">
-        <v>1.146687955375158</v>
+        <v>1.146687955375137</v>
       </c>
       <c r="F107">
-        <v>-0.7187304043397724</v>
+        <v>-0.7187304043398047</v>
       </c>
       <c r="G107">
-        <v>-1.174494771104692</v>
+        <v>-1.174494771104693</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>2.289802970562413</v>
+        <v>2.289802970562414</v>
       </c>
       <c r="D108">
         <v>-1.057103231754104</v>
       </c>
       <c r="E108">
-        <v>-0.1289415099198576</v>
+        <v>-0.1289415099198623</v>
       </c>
       <c r="F108">
-        <v>-0.1637847218383911</v>
+        <v>-0.163784721838388</v>
       </c>
       <c r="G108">
-        <v>-0.2779190643186449</v>
+        <v>-0.2779190643186456</v>
       </c>
     </row>
     <row r="109">
@@ -3292,16 +3292,16 @@
         </is>
       </c>
       <c r="C109">
-        <v>1.790507287049542</v>
+        <v>1.790507287049543</v>
       </c>
       <c r="D109">
-        <v>2.257851013254006</v>
+        <v>2.257851013254008</v>
       </c>
       <c r="E109">
-        <v>-1.060791738617862</v>
+        <v>-1.060791738617865</v>
       </c>
       <c r="F109">
-        <v>-0.0913707159986239</v>
+        <v>-0.09137071599859761</v>
       </c>
       <c r="G109">
         <v>1.770001453053974</v>
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-5.182944760151804</v>
+        <v>-5.182944760151806</v>
       </c>
       <c r="D110">
-        <v>-0.2564912356712996</v>
+        <v>-0.2564912356713009</v>
       </c>
       <c r="E110">
-        <v>0.3389172114834485</v>
+        <v>0.3389172114834597</v>
       </c>
       <c r="F110">
-        <v>0.4440610804327414</v>
+        <v>0.4440610804327297</v>
       </c>
       <c r="G110">
-        <v>-1.420453945764344</v>
+        <v>-1.420453945764345</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>2.673491410676558</v>
+        <v>2.673491410676559</v>
       </c>
       <c r="D111">
-        <v>1.864704538249218</v>
+        <v>1.86470453824922</v>
       </c>
       <c r="E111">
-        <v>-1.219924251724967</v>
+        <v>-1.219924251724956</v>
       </c>
       <c r="F111">
-        <v>0.399849431117779</v>
+        <v>0.3998494311178087</v>
       </c>
       <c r="G111">
-        <v>-0.476748148239406</v>
+        <v>-0.4767481482394071</v>
       </c>
     </row>
     <row r="112">
@@ -3373,16 +3373,16 @@
         </is>
       </c>
       <c r="C112">
-        <v>2.494391554069114</v>
+        <v>2.494391554069116</v>
       </c>
       <c r="D112">
         <v>-1.065613392560309</v>
       </c>
       <c r="E112">
-        <v>-0.7521542983778505</v>
+        <v>-0.7521542983778275</v>
       </c>
       <c r="F112">
-        <v>0.8873686339879316</v>
+        <v>0.8873686339879522</v>
       </c>
       <c r="G112">
         <v>1.155448980497105</v>
@@ -3403,16 +3403,16 @@
         <v>-1.861245236023531</v>
       </c>
       <c r="D113">
-        <v>-1.717333026715279</v>
+        <v>-1.717333026715278</v>
       </c>
       <c r="E113">
-        <v>-1.914828385488235</v>
+        <v>-1.914828385488164</v>
       </c>
       <c r="F113">
-        <v>2.734622244961262</v>
+        <v>2.734622244961313</v>
       </c>
       <c r="G113">
-        <v>0.5505659130579688</v>
+        <v>0.5505659130579698</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-6.243081038298478</v>
+        <v>-6.24308103829848</v>
       </c>
       <c r="D114">
-        <v>-2.098006159215791</v>
+        <v>-2.098006159215795</v>
       </c>
       <c r="E114">
-        <v>-0.5119061991278441</v>
+        <v>-0.5119061991279199</v>
       </c>
       <c r="F114">
-        <v>-2.800622746570378</v>
+        <v>-2.800622746570365</v>
       </c>
       <c r="G114">
-        <v>0.717516520919161</v>
+        <v>0.7175165209191626</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-7.745781990408351</v>
+        <v>-7.745781990408358</v>
       </c>
       <c r="D115">
-        <v>2.480857828291919</v>
+        <v>2.480857828291917</v>
       </c>
       <c r="E115">
-        <v>-2.341408555647951</v>
+        <v>-2.341408555647944</v>
       </c>
       <c r="F115">
-        <v>0.2417308767498218</v>
+        <v>0.2417308767498801</v>
       </c>
       <c r="G115">
-        <v>0.9401653196668825</v>
+        <v>0.9401653196668832</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>2.288302367476203</v>
+        <v>2.288302367476204</v>
       </c>
       <c r="D116">
         <v>-1.599607462959485</v>
       </c>
       <c r="E116">
-        <v>1.755202098430637</v>
+        <v>1.755202098430672</v>
       </c>
       <c r="F116">
-        <v>1.315201456123596</v>
+        <v>1.31520145612355</v>
       </c>
       <c r="G116">
-        <v>-0.558173134213671</v>
+        <v>-0.5581731342136714</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-1.125619081341348</v>
+        <v>-1.125619081341349</v>
       </c>
       <c r="D117">
-        <v>0.7293513341710426</v>
+        <v>0.7293513341710429</v>
       </c>
       <c r="E117">
-        <v>-0.3345520398004007</v>
+        <v>-0.3345520398003761</v>
       </c>
       <c r="F117">
-        <v>0.9492975041731213</v>
+        <v>0.9492975041731272</v>
       </c>
       <c r="G117">
-        <v>0.009150459971391222</v>
+        <v>0.009150459971390003</v>
       </c>
     </row>
     <row r="118">
@@ -3535,16 +3535,16 @@
         </is>
       </c>
       <c r="C118">
-        <v>2.58402285201389</v>
+        <v>2.584022852013891</v>
       </c>
       <c r="D118">
-        <v>3.030513933659056</v>
+        <v>3.030513933659057</v>
       </c>
       <c r="E118">
-        <v>-3.223118860122925</v>
+        <v>-3.223118860122932</v>
       </c>
       <c r="F118">
-        <v>-0.2369794594319741</v>
+        <v>-0.2369794594318921</v>
       </c>
       <c r="G118">
         <v>1.113101622277223</v>
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.7588558599326675</v>
+        <v>-0.7588558599326671</v>
       </c>
       <c r="D119">
         <v>-2.052548600011182</v>
       </c>
       <c r="E119">
-        <v>0.8348854294064157</v>
+        <v>0.8348854294064381</v>
       </c>
       <c r="F119">
-        <v>0.8399468918764633</v>
+        <v>0.8399468918764421</v>
       </c>
       <c r="G119">
-        <v>-0.6575224420737447</v>
+        <v>-0.6575224420737438</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>3.071406861965159</v>
+        <v>3.071406861965161</v>
       </c>
       <c r="D120">
-        <v>-0.2309185716330237</v>
+        <v>-0.2309185716330239</v>
       </c>
       <c r="E120">
-        <v>0.3526588020162107</v>
+        <v>0.3526588020161646</v>
       </c>
       <c r="F120">
-        <v>-1.687243293614413</v>
+        <v>-1.687243293614422</v>
       </c>
       <c r="G120">
-        <v>0.2988808454635192</v>
+        <v>0.2988808454635203</v>
       </c>
     </row>
     <row r="121">
@@ -3619,16 +3619,16 @@
         <v>-10.38639614286582</v>
       </c>
       <c r="D121">
-        <v>0.04499096150525165</v>
+        <v>0.04499096150524312</v>
       </c>
       <c r="E121">
-        <v>0.03988011633142822</v>
+        <v>0.03988011633124944</v>
       </c>
       <c r="F121">
-        <v>-6.696273767249248</v>
+        <v>-6.69627376724925</v>
       </c>
       <c r="G121">
-        <v>0.3534668974391409</v>
+        <v>0.3534668974391415</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>0.7238371516204132</v>
+        <v>0.7238371516204137</v>
       </c>
       <c r="D122">
-        <v>-0.936536017632741</v>
+        <v>-0.9365360176327405</v>
       </c>
       <c r="E122">
-        <v>0.9473271866610036</v>
+        <v>0.9473271866610334</v>
       </c>
       <c r="F122">
-        <v>1.159274612149602</v>
+        <v>1.159274612149576</v>
       </c>
       <c r="G122">
-        <v>-0.3081996812584186</v>
+        <v>-0.3081996812584189</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.3191702434349735</v>
+        <v>0.3191702434349739</v>
       </c>
       <c r="D123">
-        <v>-0.9391594256406151</v>
+        <v>-0.9391594256406158</v>
       </c>
       <c r="E123">
-        <v>-1.572017544469863</v>
+        <v>-1.572017544469849</v>
       </c>
       <c r="F123">
-        <v>0.5247040993865293</v>
+        <v>0.5247040993865706</v>
       </c>
       <c r="G123">
-        <v>0.1190405475137523</v>
+        <v>0.1190405475137525</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-0.4742514665773517</v>
+        <v>-0.4742514665773516</v>
       </c>
       <c r="D124">
-        <v>-0.2231700057144475</v>
+        <v>-0.2231700057144478</v>
       </c>
       <c r="E124">
-        <v>0.5966723985644546</v>
+        <v>0.596672398564464</v>
       </c>
       <c r="F124">
-        <v>0.4048632096847075</v>
+        <v>0.404863209684692</v>
       </c>
       <c r="G124">
-        <v>0.9835404193419527</v>
+        <v>0.9835404193419541</v>
       </c>
     </row>
     <row r="125">
@@ -3724,16 +3724,16 @@
         </is>
       </c>
       <c r="C125">
-        <v>-4.830642999749934</v>
+        <v>-4.830642999749935</v>
       </c>
       <c r="D125">
-        <v>-1.864477352553214</v>
+        <v>-1.864477352553217</v>
       </c>
       <c r="E125">
-        <v>-1.94335728581281</v>
+        <v>-1.943357285812763</v>
       </c>
       <c r="F125">
-        <v>1.798939729888964</v>
+        <v>1.798939729889012</v>
       </c>
       <c r="G125">
         <v>-1.244646957605166</v>
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-5.100130427556863</v>
+        <v>-5.100130427556864</v>
       </c>
       <c r="D126">
-        <v>-1.169199534506237</v>
+        <v>-1.169199534506238</v>
       </c>
       <c r="E126">
-        <v>0.04268807279745974</v>
+        <v>0.04268807279752436</v>
       </c>
       <c r="F126">
-        <v>2.460255117315279</v>
+        <v>2.460255117315276</v>
       </c>
       <c r="G126">
-        <v>0.06214825025628808</v>
+        <v>0.06214825025628884</v>
       </c>
     </row>
   </sheetData>
